--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488029_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488029_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9557</v>
+        <v>4.7625</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6644</v>
+        <v>6.3028</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7088</v>
+        <v>-1.5403</v>
       </c>
       <c r="G2" t="n">
         <v>5.2127</v>
@@ -610,13 +610,13 @@
         <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2702</v>
+        <v>0.077</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1727</v>
+        <v>-0.1889</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0975</v>
+        <v>0.266</v>
       </c>
       <c r="V2" t="n">
         <v>0.0674</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.391</v>
+        <v>3.6176</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2722</v>
+        <v>2.4988</v>
       </c>
       <c r="F3" t="n">
         <v>1.1188</v>
@@ -688,10 +688,10 @@
         <v>2.7751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7526</v>
+        <v>-0.5259</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8736</v>
+        <v>-0.6469</v>
       </c>
       <c r="U3" t="n">
         <v>0.121</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GARCIA GUERRERO</t>
+          <t>A. BUALO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.21</v>
+        <v>1.4711</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6479</v>
+        <v>3.5899</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5621</v>
+        <v>-2.1189</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4855</v>
+        <v>2.889</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6107</v>
+        <v>0.5128</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0962</v>
+        <v>2.3762</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1471</v>
+        <v>5.5439</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4641</v>
+        <v>2.5228</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6830000000000001</v>
+        <v>3.0211</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6617</v>
+        <v>-2.6548</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0748</v>
+        <v>-2.0099</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4132</v>
+        <v>-0.6449</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5858</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5947</v>
+        <v>0.2184</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4992</v>
+        <v>-0.4037</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0955</v>
+        <v>0.6221</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2666</v>
+        <v>0.9405</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4142</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2666</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BUALO</t>
+          <t>A. GARCIA GUERRERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8202</v>
+        <v>1.3348</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9953</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.175</v>
+        <v>0.5621</v>
       </c>
       <c r="G6" t="n">
-        <v>2.889</v>
+        <v>0.4855</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5128</v>
+        <v>-0.6107</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3762</v>
+        <v>1.0962</v>
       </c>
       <c r="J6" t="n">
-        <v>5.5439</v>
+        <v>1.1471</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5228</v>
+        <v>0.4641</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0211</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.6548</v>
+        <v>-0.6617</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0099</v>
+        <v>-1.0748</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6449</v>
+        <v>0.4132</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.5769</v>
+        <v>1.5858</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4324</v>
+        <v>-0.4699</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9984</v>
+        <v>-0.3744</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5659</v>
+        <v>-0.0955</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9405</v>
+        <v>-0.2666</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4142</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4737</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0363</v>
+        <v>0.0876</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5319</v>
+        <v>0.5154</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5682</v>
+        <v>-0.4278</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9191</v>
@@ -1000,13 +1000,13 @@
         <v>1.9822</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1781</v>
+        <v>0.3019</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.132</v>
+        <v>-0.1486</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3101</v>
+        <v>0.4505</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2775</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.4067</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2142</v>
+        <v>-1.1518</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5766</v>
+        <v>0.7451</v>
       </c>
       <c r="G8" t="n">
         <v>0.8932</v>
@@ -1078,13 +1078,13 @@
         <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.07489999999999999</v>
+        <v>0.156</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1872</v>
+        <v>-0.1248</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1123</v>
+        <v>0.2808</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2666</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8969</v>
+        <v>-1.0444</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0755</v>
+        <v>-0.3353</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8214</v>
+        <v>-0.7091</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4063</v>
@@ -1156,13 +1156,13 @@
         <v>2.9733</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0456</v>
+        <v>-0.1019</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0145</v>
+        <v>-0.2742</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0601</v>
+        <v>0.1724</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5362</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7769</v>
+        <v>-4.8591</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3992</v>
+        <v>-3.1726</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3777</v>
+        <v>-1.6866</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3226</v>
@@ -1234,13 +1234,13 @@
         <v>0.9911</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2712</v>
+        <v>0.189</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4992</v>
+        <v>-0.2725</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7704</v>
+        <v>0.4615</v>
       </c>
       <c r="V10" t="n">
         <v>-1.7433</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.4987</v>
+        <v>-6.5477</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.3266</v>
+        <v>-5.1229</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1721</v>
+        <v>-1.4248</v>
       </c>
       <c r="G11" t="n">
         <v>-3.8551</v>
@@ -1312,13 +1312,13 @@
         <v>0.1982</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3307</v>
+        <v>0.2817</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4368</v>
+        <v>-0.233</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7675</v>
+        <v>0.5148</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1992</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.1951</v>
+        <v>-10.5204</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.8312</v>
+        <v>-6.0723</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.3638</v>
+        <v>-4.4481</v>
       </c>
       <c r="G12" t="n">
         <v>-7.2806</v>
@@ -1390,13 +1390,13 @@
         <v>1.784</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9114</v>
+        <v>-0.2367</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2479</v>
+        <v>-0.489</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3365</v>
+        <v>0.2523</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8137</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.8486</v>
+        <v>-10.2887</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.918999999999999</v>
+        <v>-0.3593000000000011</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.929500000000001</v>
+        <v>-9.929600000000001</v>
       </c>
       <c r="G13" t="n">
         <v>0.01780000000000115</v>
@@ -1468,19 +1468,19 @@
         <v>16.8489</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6702</v>
+        <v>-0.1104</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.716099999999999</v>
+        <v>-3.156</v>
       </c>
       <c r="U13" t="n">
-        <v>3.0458</v>
+        <v>3.0459</v>
       </c>
       <c r="V13" t="n">
         <v>-6.2319</v>
       </c>
       <c r="W13" t="n">
-        <v>4.3505</v>
+        <v>4.350499999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-10.5825</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9743</v>
+        <v>6.4203</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8046</v>
+        <v>4.1103</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1697</v>
+        <v>2.3101</v>
       </c>
       <c r="G14" t="n">
         <v>1.9361</v>
@@ -1546,13 +1546,13 @@
         <v>2.9733</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3763</v>
+        <v>0.0697</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8001</v>
+        <v>-0.4945</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4239</v>
+        <v>0.5642</v>
       </c>
       <c r="V14" t="n">
         <v>2.6305</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MUNOZ LEIVA</t>
+          <t>P. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8281</v>
+        <v>3.1013</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2373</v>
+        <v>2.4062</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4092</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4946</v>
+        <v>2.5685</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0295</v>
+        <v>-0.0488</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5241</v>
+        <v>2.6173</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5463</v>
+        <v>4.2879</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3052</v>
+        <v>1.1501</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2411</v>
+        <v>3.1377</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0517</v>
+        <v>-1.7194</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3347</v>
+        <v>-1.1989</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2831</v>
+        <v>-0.5205</v>
       </c>
       <c r="P15" t="n">
-        <v>2.7751</v>
+        <v>1.1893</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7751</v>
+        <v>3.1716</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8267</v>
+        <v>0.4047</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4244</v>
+        <v>-0.166</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4022</v>
+        <v>0.5707</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.2684</v>
+        <v>-1.0612</v>
       </c>
       <c r="W15" t="n">
         <v>0.2666</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.5349</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.648</v>
+        <v>2.5076</v>
       </c>
       <c r="E16" t="n">
         <v>1.7187</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9293</v>
+        <v>0.7889</v>
       </c>
       <c r="G16" t="n">
         <v>1.63</v>
@@ -1702,13 +1702,13 @@
         <v>0.7929</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0091</v>
+        <v>-0.1313</v>
       </c>
       <c r="T16" t="n">
         <v>-0.2496</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2587</v>
+        <v>0.1183</v>
       </c>
       <c r="V16" t="n">
         <v>1.2071</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4453</v>
+        <v>2.2102</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4059</v>
+        <v>1.5078</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0394</v>
+        <v>0.7024</v>
       </c>
       <c r="G17" t="n">
         <v>0.356</v>
@@ -1780,13 +1780,13 @@
         <v>2.5769</v>
       </c>
       <c r="S17" t="n">
-        <v>0.994</v>
+        <v>0.7589</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2458</v>
+        <v>-0.1439</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2398</v>
+        <v>0.9029</v>
       </c>
       <c r="V17" t="n">
         <v>1.6899</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ SANCHEZ</t>
+          <t>J. MUNOZ LEIVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1989</v>
+        <v>1.876</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8969</v>
+        <v>2.1167</v>
       </c>
       <c r="F18" t="n">
-        <v>0.302</v>
+        <v>-0.2407</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5685</v>
+        <v>0.4946</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0488</v>
+        <v>-0.0295</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6173</v>
+        <v>0.5241</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2879</v>
+        <v>1.5463</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1501</v>
+        <v>1.3052</v>
       </c>
       <c r="L18" t="n">
-        <v>3.1377</v>
+        <v>0.2411</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7194</v>
+        <v>-1.0517</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1989</v>
+        <v>-1.3347</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5205</v>
+        <v>0.2831</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1893</v>
+        <v>2.7751</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1716</v>
+        <v>2.7751</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4977</v>
+        <v>0.8746</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6753</v>
+        <v>0.3039</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1776</v>
+        <v>0.5707</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0612</v>
+        <v>-2.2684</v>
       </c>
       <c r="W18" t="n">
         <v>0.2666</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3278</v>
+        <v>-2.5349</v>
       </c>
     </row>
     <row r="19">
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.148</v>
+        <v>-0.0461</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1891</v>
+        <v>-0.0872</v>
       </c>
       <c r="F23" t="n">
         <v>0.0411</v>
@@ -2248,10 +2248,10 @@
         <v>0.5947</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0624</v>
+        <v>0.1643</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2496</v>
+        <v>-0.1477</v>
       </c>
       <c r="U23" t="n">
         <v>0.312</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3797</v>
+        <v>-0.1936</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1726</v>
+        <v>0.2745</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5524</v>
+        <v>-0.4681</v>
       </c>
       <c r="G24" t="n">
         <v>-0.458</v>
@@ -2326,13 +2326,13 @@
         <v>0.5947</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5164</v>
+        <v>-0.3303</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4368</v>
+        <v>-0.3349</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.0046</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.0484</v>
+        <v>-1.0131</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3515</v>
+        <v>-1.1478</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3031</v>
+        <v>0.1347</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1835</v>
@@ -2404,13 +2404,13 @@
         <v>0.5947</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3245</v>
+        <v>0.3597</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2496</v>
+        <v>-0.0459</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.4056</v>
       </c>
       <c r="V25" t="n">
         <v>1.2071</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. MUNOZ MENDOZA</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.3967</v>
+        <v>-1.5848</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0068</v>
+        <v>0.1771</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3899</v>
+        <v>-1.7619</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.8609</v>
+        <v>0.2904</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5044</v>
+        <v>-0.031</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.3564</v>
+        <v>0.3214</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0738</v>
+        <v>3.496</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6324</v>
+        <v>2.2466</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5586</v>
+        <v>1.2494</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.9347</v>
+        <v>-3.2056</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.1369</v>
+        <v>-2.2776</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.928</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5947</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.1982</v>
+        <v>-4.1627</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7929</v>
+        <v>1.784</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7396</v>
+        <v>-0.6332</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1176</v>
+        <v>-0.8965</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6221</v>
+        <v>0.2633</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.8701</v>
+        <v>1.1367</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.8701</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>J. VERKERK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,73 +2515,73 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.827</v>
+        <v>-1.706</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0752</v>
+        <v>-2.9684</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.9023</v>
+        <v>1.2624</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2904</v>
+        <v>-2.7194</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.031</v>
+        <v>-0.7126</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3214</v>
+        <v>-2.0068</v>
       </c>
       <c r="J27" t="n">
-        <v>3.496</v>
+        <v>0.0827</v>
       </c>
       <c r="K27" t="n">
-        <v>2.2466</v>
+        <v>1.4332</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2494</v>
+        <v>-1.3505</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.2056</v>
+        <v>-2.8021</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.2776</v>
+        <v>-2.1457</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.928</v>
+        <v>-0.6563</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.3787</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4.1627</v>
+        <v>-3.9645</v>
       </c>
       <c r="R27" t="n">
-        <v>1.784</v>
+        <v>2.5769</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.8754999999999999</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9984</v>
+        <v>0.0433</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1229</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>1.1367</v>
+        <v>1.7604</v>
       </c>
       <c r="W27" t="n">
-        <v>1.7403</v>
+        <v>0.8701</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.6036</v>
+        <v>0.8902</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>J. VERKERK</t>
+          <t>J. MUNOZ MENDOZA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2593,67 +2593,67 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.9482</v>
+        <v>-2.2254</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.0703</v>
+        <v>-0.4143</v>
       </c>
       <c r="F28" t="n">
-        <v>1.122</v>
+        <v>-1.8111</v>
       </c>
       <c r="G28" t="n">
-        <v>-2.7194</v>
+        <v>-1.8609</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7126</v>
+        <v>-0.5044</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.0068</v>
+        <v>-1.3564</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0827</v>
+        <v>0.0738</v>
       </c>
       <c r="K28" t="n">
-        <v>1.4332</v>
+        <v>0.6324</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.3505</v>
+        <v>-0.5586</v>
       </c>
       <c r="M28" t="n">
-        <v>-2.8021</v>
+        <v>-1.9347</v>
       </c>
       <c r="N28" t="n">
-        <v>-2.1457</v>
+        <v>-1.1369</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.6563</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P28" t="n">
-        <v>-1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="Q28" t="n">
-        <v>-3.9645</v>
+        <v>-0.1982</v>
       </c>
       <c r="R28" t="n">
-        <v>2.5769</v>
+        <v>0.7929</v>
       </c>
       <c r="S28" t="n">
-        <v>0.3983</v>
+        <v>-0.089</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.0586</v>
+        <v>-0.2899</v>
       </c>
       <c r="U28" t="n">
-        <v>0.4569</v>
+        <v>0.2009</v>
       </c>
       <c r="V28" t="n">
-        <v>1.7604</v>
+        <v>-0.8701</v>
       </c>
       <c r="W28" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0.8902</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="29">
@@ -2671,22 +2671,22 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>11.84890000000001</v>
+        <v>11.8487</v>
       </c>
       <c r="E29" t="n">
-        <v>9.929600000000001</v>
+        <v>9.929699999999997</v>
       </c>
       <c r="F29" t="n">
-        <v>1.919000000000001</v>
+        <v>1.9191</v>
       </c>
       <c r="G29" t="n">
         <v>-0.01770000000000005</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7183999999999998</v>
+        <v>0.7183999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7360999999999995</v>
+        <v>-0.7360999999999993</v>
       </c>
       <c r="J29" t="n">
         <v>19.2421</v>
@@ -2695,7 +2695,7 @@
         <v>14.0656</v>
       </c>
       <c r="L29" t="n">
-        <v>5.176499999999999</v>
+        <v>5.176500000000001</v>
       </c>
       <c r="M29" t="n">
         <v>-19.2599</v>
@@ -2707,22 +2707,22 @@
         <v>-5.912500000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>3.964499999999998</v>
+        <v>3.964499999999999</v>
       </c>
       <c r="Q29" t="n">
         <v>-16.8489</v>
       </c>
       <c r="R29" t="n">
-        <v>20.8135</v>
+        <v>20.81349999999999</v>
       </c>
       <c r="S29" t="n">
         <v>1.6702</v>
       </c>
       <c r="T29" t="n">
-        <v>-3.0458</v>
+        <v>-3.0457</v>
       </c>
       <c r="U29" t="n">
-        <v>4.715999999999999</v>
+        <v>4.716</v>
       </c>
       <c r="V29" t="n">
         <v>6.231700000000001</v>
